--- a/data/trans_orig/P33B4_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B4_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que se siente cansado cuando despierta por la mañana en 2023</t>
+          <t>Población según la frecuencia con la que se siente cansado cuando despierta por la mañana en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19527</t>
+          <t>20469</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12669</t>
+          <t>12896</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26442</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20967</t>
+          <t>21150</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40608</t>
+          <t>40293</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41994</t>
+          <t>41197</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35572</t>
+          <t>35623</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54274</t>
+          <t>54250</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59347</t>
+          <t>59394</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87620</t>
+          <t>87728</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>256766</t>
+          <t>256475</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>281899</t>
+          <t>282225</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>211124</t>
+          <t>210979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>233952</t>
+          <t>234071</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>475522</t>
+          <t>477303</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>510151</t>
+          <t>510318</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,9%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25380</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>24983</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42891</t>
+          <t>44005</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t>35940</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61793</t>
+          <t>62083</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13293</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33304</t>
+          <t>33564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29108</t>
+          <t>28616</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49307</t>
+          <t>49751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47901</t>
+          <t>48300</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76709</t>
+          <t>76924</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66967</t>
+          <t>68467</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106240</t>
+          <t>107882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,47 +1540,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>20,81%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>105403</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>92084</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>122127</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>20,49%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>105403</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>91130</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>121273</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>20,49%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165119</t>
+          <t>168848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>217271</t>
+          <t>221114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>371877</t>
+          <t>371083</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>417105</t>
+          <t>415500</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>318016</t>
+          <t>316752</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>356862</t>
+          <t>354965</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>703934</t>
+          <t>702495</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>763187</t>
+          <t>760009</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18795</t>
+          <t>19084</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38010</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32417</t>
+          <t>33502</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53563</t>
+          <t>53611</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56351</t>
+          <t>56851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83882</t>
+          <t>83325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35130</t>
+          <t>34965</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19786</t>
+          <t>20114</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35138</t>
+          <t>36109</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>40418</t>
+          <t>40834</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>65284</t>
+          <t>64124</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11491</t>
+          <t>11807</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25512</t>
+          <t>26441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29965</t>
+          <t>30540</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48958</t>
+          <t>48986</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45303</t>
+          <t>45774</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70270</t>
+          <t>69784</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>230145</t>
+          <t>231464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>257403</t>
+          <t>258962</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>225051</t>
+          <t>226960</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>255036</t>
+          <t>256247</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>463841</t>
+          <t>464381</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>505194</t>
+          <t>505015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16856</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41051</t>
+          <t>39972</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30910</t>
+          <t>33894</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73611</t>
+          <t>74529</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60989</t>
+          <t>56459</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106369</t>
+          <t>103338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>19803</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47594</t>
+          <t>47103</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27010</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60206</t>
+          <t>59918</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>50310</t>
+          <t>53376</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96292</t>
+          <t>96888</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>21798</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>44893</t>
+          <t>44859</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46729</t>
+          <t>48723</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>103564</t>
+          <t>103422</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>81043</t>
+          <t>81978</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>136386</t>
+          <t>133767</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>203224</t>
+          <t>204580</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>239350</t>
+          <t>242442</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>248592</t>
+          <t>247671</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>368985</t>
+          <t>367002</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>477040</t>
+          <t>476309</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>600379</t>
+          <t>593162</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,29%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>19525</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16289</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10342</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>18540</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33007</t>
+          <t>32173</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>109510</t>
+          <t>108137</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131734</t>
+          <t>131539</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>141268</t>
+          <t>139185</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>160008</t>
+          <t>159521</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>256247</t>
+          <t>256183</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>285597</t>
+          <t>284855</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>33023</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>53845</t>
+          <t>55421</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24906</t>
+          <t>25431</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42541</t>
+          <t>42991</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>63360</t>
+          <t>63630</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>91300</t>
+          <t>91547</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10456</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>23893</t>
+          <t>24960</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19633</t>
+          <t>19261</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34388</t>
+          <t>33753</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>34225</t>
+          <t>33401</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54642</t>
+          <t>53100</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>15733</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>31431</t>
+          <t>30247</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29073</t>
+          <t>28408</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>46115</t>
+          <t>44726</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>48521</t>
+          <t>48462</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>72360</t>
+          <t>69795</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19668</t>
+          <t>20260</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37988</t>
+          <t>37513</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>29338</t>
+          <t>29912</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45153</t>
+          <t>45596</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>52980</t>
+          <t>52936</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>76703</t>
+          <t>76763</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>189355</t>
+          <t>189991</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>215064</t>
+          <t>214762</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>145817</t>
+          <t>144730</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>169912</t>
+          <t>168868</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>343906</t>
+          <t>345528</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>378391</t>
+          <t>379548</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,06%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>25548</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>58617</t>
+          <t>57431</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>38159</t>
+          <t>37161</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>112077</t>
+          <t>112274</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>71889</t>
+          <t>78616</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>149226</t>
+          <t>148487</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>35113</t>
+          <t>34786</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>66096</t>
+          <t>64819</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>52470</t>
+          <t>47183</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>131538</t>
+          <t>134549</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>92449</t>
+          <t>94803</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>176846</t>
+          <t>178553</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>114187</t>
+          <t>113782</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>167297</t>
+          <t>166488</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>77872</t>
+          <t>69301</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>202004</t>
+          <t>201521</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>168396</t>
+          <t>187038</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>342332</t>
+          <t>344956</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>366479</t>
+          <t>364247</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>427085</t>
+          <t>424395</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>414795</t>
+          <t>415154</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>673399</t>
+          <t>687931</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>827929</t>
+          <t>819830</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1148513</t>
+          <t>1104792</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>43210</t>
+          <t>45894</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>144574</t>
+          <t>145683</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>128866</t>
+          <t>128081</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>162441</t>
+          <t>163158</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>148997</t>
+          <t>149468</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>299303</t>
+          <t>298251</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>16792</t>
+          <t>20692</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>63973</t>
+          <t>63539</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>68070</t>
+          <t>69047</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>101316</t>
+          <t>101286</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>77853</t>
+          <t>76719</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>155645</t>
+          <t>157105</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>34737</t>
+          <t>37160</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>125109</t>
+          <t>125740</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>97505</t>
+          <t>96400</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>130331</t>
+          <t>128926</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>124695</t>
+          <t>119508</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>242454</t>
+          <t>242725</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>606760</t>
+          <t>605377</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>826807</t>
+          <t>824157</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>350347</t>
+          <t>352737</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>396756</t>
+          <t>396905</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>958891</t>
+          <t>959901</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1281635</t>
+          <t>1303874</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>181082</t>
+          <t>177369</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>269016</t>
+          <t>263324</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>322468</t>
+          <t>325484</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>439173</t>
+          <t>442484</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>542694</t>
+          <t>539818</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>685879</t>
+          <t>688374</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>166969</t>
+          <t>165236</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>252133</t>
+          <t>245787</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>291459</t>
+          <t>294772</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>395914</t>
+          <t>398918</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>492553</t>
+          <t>489633</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>629771</t>
+          <t>628626</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>416153</t>
+          <t>420911</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>600399</t>
+          <t>596419</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>558095</t>
+          <t>593034</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>776492</t>
+          <t>780988</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1101163</t>
+          <t>1082395</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1350563</t>
+          <t>1353174</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2376978</t>
+          <t>2386119</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2696543</t>
+          <t>2698960</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2069052</t>
+          <t>2063538</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2499607</t>
+          <t>2469347</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4493867</t>
+          <t>4487466</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4959207</t>
+          <t>5001639</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>70,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B4_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B4_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>11587</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20469</t>
+          <t>18931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>20246</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12896</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25803</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>31833</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21150</t>
+          <t>23755</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40293</t>
+          <t>42168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28384</t>
+          <t>34825</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19925</t>
+          <t>25214</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41197</t>
+          <t>46090</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44118</t>
+          <t>52089</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35623</t>
+          <t>42229</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54250</t>
+          <t>64227</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>72501</t>
+          <t>86913</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59394</t>
+          <t>73219</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87728</t>
+          <t>102772</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>271024</t>
+          <t>271628</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>256475</t>
+          <t>259646</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>282225</t>
+          <t>283123</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>223034</t>
+          <t>239851</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>210979</t>
+          <t>226920</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>234071</t>
+          <t>252228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>494058</t>
+          <t>511479</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>477303</t>
+          <t>494196</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>510318</t>
+          <t>528172</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15049</t>
+          <t>15218</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>8063</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25709</t>
+          <t>25866</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32801</t>
+          <t>32966</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24983</t>
+          <t>23404</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44005</t>
+          <t>43276</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>47849</t>
+          <t>48184</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35940</t>
+          <t>36562</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>62083</t>
+          <t>62482</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22664</t>
+          <t>22710</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>34923</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>38586</t>
+          <t>40100</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28616</t>
+          <t>30634</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49751</t>
+          <t>51951</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>61250</t>
+          <t>62810</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48300</t>
+          <t>49466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76924</t>
+          <t>78584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85624</t>
+          <t>88338</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68467</t>
+          <t>69327</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107882</t>
+          <t>109570</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>105403</t>
+          <t>111535</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92084</t>
+          <t>96026</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122127</t>
+          <t>127697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>191027</t>
+          <t>199873</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168848</t>
+          <t>176040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221114</t>
+          <t>228115</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -1633,17 +1633,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>395053</t>
+          <t>404381</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>371083</t>
+          <t>381239</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415500</t>
+          <t>426078</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>337533</t>
+          <t>361153</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>316752</t>
+          <t>342885</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>354965</t>
+          <t>380096</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>732585</t>
+          <t>765533</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>702495</t>
+          <t>732536</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>760009</t>
+          <t>794844</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,84%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514322</t>
+          <t>545754</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514322</t>
+          <t>545754</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514322</t>
+          <t>545754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1032712</t>
+          <t>1076401</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1032712</t>
+          <t>1076401</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1032712</t>
+          <t>1076401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27017</t>
+          <t>27908</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19084</t>
+          <t>19357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38114</t>
+          <t>38093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41987</t>
+          <t>43369</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33502</t>
+          <t>34382</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53611</t>
+          <t>55028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>69004</t>
+          <t>71277</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56851</t>
+          <t>58398</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83325</t>
+          <t>86742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24186</t>
+          <t>25303</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34965</t>
+          <t>35823</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27565</t>
+          <t>28626</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20114</t>
+          <t>20785</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36109</t>
+          <t>37649</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>51751</t>
+          <t>53929</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>40834</t>
+          <t>42425</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64124</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17853</t>
+          <t>18228</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26441</t>
+          <t>26785</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>39321</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30540</t>
+          <t>30750</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48986</t>
+          <t>49373</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>56640</t>
+          <t>57549</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45774</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69784</t>
+          <t>70167</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>245010</t>
+          <t>242588</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>231464</t>
+          <t>227492</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>258962</t>
+          <t>255846</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>240789</t>
+          <t>245065</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>226960</t>
+          <t>230134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256247</t>
+          <t>258115</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>485799</t>
+          <t>487654</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>464381</t>
+          <t>467583</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>505015</t>
+          <t>506887</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>314065</t>
+          <t>314027</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>314065</t>
+          <t>314027</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>314065</t>
+          <t>314027</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>663193</t>
+          <t>670409</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>663193</t>
+          <t>670409</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>663193</t>
+          <t>670409</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>26616</t>
+          <t>30808</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>18585</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39972</t>
+          <t>48944</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>55101</t>
+          <t>60597</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33894</t>
+          <t>47939</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74529</t>
+          <t>75945</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>81717</t>
+          <t>91404</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56459</t>
+          <t>74375</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103338</t>
+          <t>114544</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>30658</t>
+          <t>33728</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19803</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47103</t>
+          <t>49008</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>44120</t>
+          <t>48327</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>38498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59918</t>
+          <t>62059</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>74778</t>
+          <t>82055</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53376</t>
+          <t>65267</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96888</t>
+          <t>103799</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31364</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>23477</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>44859</t>
+          <t>49522</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>79913</t>
+          <t>86453</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48723</t>
+          <t>72453</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>103422</t>
+          <t>102878</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>111277</t>
+          <t>120534</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>81978</t>
+          <t>102171</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>133767</t>
+          <t>139978</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>223919</t>
+          <t>274529</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>204580</t>
+          <t>251254</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>242442</t>
+          <t>296680</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>296177</t>
+          <t>226169</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>247671</t>
+          <t>205280</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>367002</t>
+          <t>245111</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>520095</t>
+          <t>500698</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>476309</t>
+          <t>471062</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>593162</t>
+          <t>529888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>66,68%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>475311</t>
+          <t>421546</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475311</t>
+          <t>421546</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475311</t>
+          <t>421546</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>787867</t>
+          <t>794691</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>787867</t>
+          <t>794691</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>787867</t>
+          <t>794691</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14270</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>15115</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19525</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16417</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>15690</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>21922</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>24730</t>
+          <t>26722</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32173</t>
+          <t>34558</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>121638</t>
+          <t>137361</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>108137</t>
+          <t>124731</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131539</t>
+          <t>149895</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>150423</t>
+          <t>161553</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>139185</t>
+          <t>150483</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>159521</t>
+          <t>171433</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>272061</t>
+          <t>298914</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>256183</t>
+          <t>282358</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>284855</t>
+          <t>314380</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>72,69%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>53017</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>33023</t>
+          <t>40916</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>55421</t>
+          <t>65421</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>33448</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25431</t>
+          <t>29824</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42991</t>
+          <t>49232</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>76246</t>
+          <t>91737</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>63630</t>
+          <t>77017</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>91547</t>
+          <t>108777</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>16420</t>
+          <t>16410</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10348</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24960</t>
+          <t>24764</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>27598</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19261</t>
+          <t>20196</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33753</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>42444</t>
+          <t>44008</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>33401</t>
+          <t>34397</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53100</t>
+          <t>55238</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>22238</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30247</t>
+          <t>30934</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>36012</t>
+          <t>36521</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28408</t>
+          <t>29326</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>44726</t>
+          <t>44557</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>58250</t>
+          <t>58346</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>48462</t>
+          <t>48204</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>69795</t>
+          <t>69956</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>27655</t>
+          <t>26553</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>19542</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37513</t>
+          <t>34893</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>37040</t>
+          <t>38476</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>29912</t>
+          <t>31224</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45596</t>
+          <t>47885</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>64695</t>
+          <t>65029</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>52936</t>
+          <t>54105</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>76763</t>
+          <t>76784</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,37%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>203323</t>
+          <t>205919</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>189991</t>
+          <t>191820</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>214762</t>
+          <t>216796</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>157980</t>
+          <t>161156</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>144730</t>
+          <t>148438</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>168868</t>
+          <t>172309</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>361303</t>
+          <t>367074</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>345528</t>
+          <t>348927</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>379548</t>
+          <t>383093</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,68%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>38671</t>
+          <t>46115</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>32475</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>57431</t>
+          <t>68648</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>79810</t>
+          <t>100089</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>37161</t>
+          <t>82112</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>112274</t>
+          <t>119152</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>118480</t>
+          <t>146205</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>78616</t>
+          <t>124382</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>148487</t>
+          <t>175676</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>48864</t>
+          <t>59126</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>34786</t>
+          <t>44642</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>64819</t>
+          <t>79827</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>96206</t>
+          <t>116091</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>47183</t>
+          <t>96325</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>134549</t>
+          <t>136033</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>145070</t>
+          <t>175217</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>94803</t>
+          <t>147264</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>178553</t>
+          <t>202358</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>137298</t>
+          <t>149161</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>113782</t>
+          <t>126081</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>166488</t>
+          <t>174043</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>147183</t>
+          <t>168261</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>69301</t>
+          <t>148099</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>201521</t>
+          <t>188230</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>284481</t>
+          <t>317421</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>187038</t>
+          <t>287657</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>344956</t>
+          <t>351014</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>398417</t>
+          <t>464203</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>364247</t>
+          <t>430027</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>424395</t>
+          <t>490884</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>526066</t>
+          <t>387616</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>415154</t>
+          <t>362308</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>687931</t>
+          <t>415009</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>924482</t>
+          <t>851819</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>819830</t>
+          <t>813131</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1104792</t>
+          <t>894203</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>59,99%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>101582</t>
+          <t>114462</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>45894</t>
+          <t>96932</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>145683</t>
+          <t>133337</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>145831</t>
+          <t>167312</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>128081</t>
+          <t>148875</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>163158</t>
+          <t>186501</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>247413</t>
+          <t>281775</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>149468</t>
+          <t>257447</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>298251</t>
+          <t>310889</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>42502</t>
+          <t>46556</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>35183</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>63539</t>
+          <t>60123</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>82028</t>
+          <t>88419</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>69047</t>
+          <t>74189</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>101286</t>
+          <t>103232</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>124531</t>
+          <t>134976</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>76719</t>
+          <t>116700</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>157105</t>
+          <t>155616</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>85855</t>
+          <t>100602</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>37160</t>
+          <t>82458</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>125740</t>
+          <t>121595</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>113148</t>
+          <t>133398</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>96400</t>
+          <t>115319</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>128926</t>
+          <t>151419</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>199003</t>
+          <t>234000</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>119508</t>
+          <t>209643</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>242725</t>
+          <t>260589</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>698781</t>
+          <t>536451</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>605377</t>
+          <t>509310</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>824157</t>
+          <t>562412</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>374385</t>
+          <t>441480</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>352737</t>
+          <t>418489</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>396905</t>
+          <t>470622</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1073166</t>
+          <t>977931</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>959901</t>
+          <t>937403</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1303874</t>
+          <t>1014838</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>62,31%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>230145</t>
+          <t>255982</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>177369</t>
+          <t>225833</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>263324</t>
+          <t>293588</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>395677</t>
+          <t>446667</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>325484</t>
+          <t>413139</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>442484</t>
+          <t>482837</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>625822</t>
+          <t>702649</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>539818</t>
+          <t>658065</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>688374</t>
+          <t>746046</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>212662</t>
+          <t>231868</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>165236</t>
+          <t>202198</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>245787</t>
+          <t>265009</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>357278</t>
+          <t>394021</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>294772</t>
+          <t>364310</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>398918</t>
+          <t>429016</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>569940</t>
+          <t>625889</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>489633</t>
+          <t>583161</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>628626</t>
+          <t>670415</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>535671</t>
+          <t>589148</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>420911</t>
+          <t>544484</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>596419</t>
+          <t>634522</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>716015</t>
+          <t>791085</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>593034</t>
+          <t>752845</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>780988</t>
+          <t>834586</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1251686</t>
+          <t>1380233</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1082395</t>
+          <t>1322087</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1353174</t>
+          <t>1450693</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2478324</t>
+          <t>2452716</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2386119</t>
+          <t>2389852</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2698960</t>
+          <t>2511758</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2189412</t>
+          <t>2101209</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2063538</t>
+          <t>2049436</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2469347</t>
+          <t>2150649</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>4667736</t>
+          <t>4553925</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4487466</t>
+          <t>4468313</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5001639</t>
+          <t>4630232</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3456802</t>
+          <t>3529714</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3658381</t>
+          <t>3732982</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7115184</t>
+          <t>7262696</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
